--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_bind.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_bind.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_bind" sheetId="1" r:id="rId1"/>
@@ -1159,7 +1159,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1"/>
     </row>
@@ -1171,7 +1171,7 @@
         <v>13</v>
       </c>
       <c r="C8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="1"/>
     </row>
@@ -1195,11 +1195,11 @@
         <v>15</v>
       </c>
       <c r="C10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" customFormat="1" ht="16.5" spans="1:3">
+    <row r="11" customFormat="1" ht="16.5" spans="1:4">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="1" ht="16.5" spans="1:3">
+    <row r="12" customFormat="1" ht="16.5" spans="1:4">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -1218,10 +1218,10 @@
         <v>17</v>
       </c>
       <c r="C12" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" ht="16.5" spans="1:3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" ht="16.5" spans="1:4">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -1229,10 +1229,10 @@
         <v>18</v>
       </c>
       <c r="C13" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" ht="16.5" spans="1:3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" ht="16.5" spans="1:4">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -1240,10 +1240,10 @@
         <v>19</v>
       </c>
       <c r="C14" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" ht="16.5" spans="1:3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" ht="16.5" spans="1:4">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1251,10 +1251,10 @@
         <v>20</v>
       </c>
       <c r="C15" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" ht="16.5" spans="1:3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" ht="16.5" spans="1:4">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>21</v>
       </c>
       <c r="C16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="1" ht="16.5" spans="1:3">
@@ -1273,7 +1273,7 @@
         <v>22</v>
       </c>
       <c r="C17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="1" ht="16.5" spans="1:3">
@@ -1283,30 +1283,30 @@
       <c r="B18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="C18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:3">
       <c r="A19">
         <v>15</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="C19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:3">
       <c r="A20">
         <v>16</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C20">
-        <v>1</v>
+      <c r="C20" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
